--- a/ig/ch-term/ch-vacd-targetdiseases-vaccines-cm.xlsx
+++ b/ig/ch-term/ch-vacd-targetdiseases-vaccines-cm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -641,6 +641,15 @@
     <t>69992</t>
   </si>
   <si>
+    <t>Influvac 0.5 ml</t>
+  </si>
+  <si>
+    <t>70144</t>
+  </si>
+  <si>
+    <t>Flucelvax</t>
+  </si>
+  <si>
     <t>63650001</t>
   </si>
   <si>
@@ -770,7 +779,7 @@
     <t>69781</t>
   </si>
   <si>
-    <t>Capvaxive, Injektionslösung in Fertigspritze MSD Merck Sharp &amp; Dohme AG</t>
+    <t>Capvaxive</t>
   </si>
   <si>
     <t>240532009</t>
@@ -788,7 +797,13 @@
     <t>65387</t>
   </si>
   <si>
-    <t>Gardasil 9</t>
+    <t>Gardasil 9 (Fertigspritze)</t>
+  </si>
+  <si>
+    <t>65728</t>
+  </si>
+  <si>
+    <t>Gardasil 9 (Durchstechflasche)</t>
   </si>
   <si>
     <t>57814</t>
@@ -947,43 +962,43 @@
     <t>69913</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 0.042 mg, Injektionsdispersion in einer Fertigspritze, Pfizer AG</t>
+    <t>Comirnaty JN.1 0.042 mg</t>
   </si>
   <si>
     <t>69912-01</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 30 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 30 µg</t>
   </si>
   <si>
     <t>69912-02</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 10 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 10 µg</t>
   </si>
   <si>
     <t>69788</t>
   </si>
   <si>
-    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml, Dispersion zur Injektion, Moderna Switzerland GmbH</t>
+    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml</t>
   </si>
   <si>
     <t>70205</t>
   </si>
   <si>
-    <t>Spikevax LP.8.1 Moderna Switzerland GmbH</t>
+    <t>Spikevax LP.8.1</t>
   </si>
   <si>
     <t>70400</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 10 μg, Injektionsdispersion Pfizer AG</t>
+    <t>Comirnaty LP.8.1 10 µg</t>
   </si>
   <si>
     <t>70403</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 30 Mikrogramm, Injektionsdispersion in einer Fertigspritze Pfizer AG'</t>
+    <t>Comirnaty LP.8.1 30 Mikrogramm</t>
   </si>
   <si>
     <t>719865001</t>
@@ -1013,7 +1028,7 @@
     <t>68358</t>
   </si>
   <si>
-    <t>Ervebo, Injektionslösung</t>
+    <t>Ervebo</t>
   </si>
   <si>
     <t>860805006</t>
@@ -1067,7 +1082,7 @@
     <t>69995-01</t>
   </si>
   <si>
-    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml, Injektionsdispersion	Moderna Switzerland GmbH</t>
+    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml</t>
   </si>
   <si>
     <t>38362002</t>
@@ -1091,7 +1106,7 @@
     <t>69863-01</t>
   </si>
   <si>
-    <t>Efluelda TIV 0.5 mL, suspension injectable en seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Efluelda TIV 0.5 mL</t>
   </si>
   <si>
     <t>442696006</t>
@@ -1110,6 +1125,18 @@
   </si>
   <si>
     <t>Influenza caused by Influenza B virus (disorder)</t>
+  </si>
+  <si>
+    <t>111864006</t>
+  </si>
+  <si>
+    <t>Chikungunya fever (disorder)</t>
+  </si>
+  <si>
+    <t>70490</t>
+  </si>
+  <si>
+    <t>Vimkunya</t>
   </si>
   <si>
     <t>111852003</t>
@@ -2036,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4331,7 +4358,7 @@
         <v>206</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136">
@@ -4348,701 +4375,701 @@
         <v>207</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="B137" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D137" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="C137" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D137" t="s" s="2">
+      <c r="E137" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="E137" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C138" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B139" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D139" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="C139" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D139" t="s" s="2">
+      <c r="E139" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="E139" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C140" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B141" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D141" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="C141" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D141" t="s" s="2">
+      <c r="E141" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="E141" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="B142" t="s" s="2">
+      <c r="C142" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D142" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="C142" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D142" t="s" s="2">
+      <c r="E142" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="E142" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>139</v>
+        <v>232</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>233</v>
+        <v>141</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="B147" t="s" s="2">
+      <c r="C147" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D147" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="C147" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D147" t="s" s="2">
+      <c r="E147" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="E147" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="B148" t="s" s="2">
+      <c r="C148" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D148" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="C148" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D148" t="s" s="2">
+      <c r="E148" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="E148" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C151" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C153" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B154" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D154" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="C154" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D154" t="s" s="2">
+      <c r="E154" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="E154" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B157" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D157" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="C157" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D157" t="s" s="2">
+      <c r="E157" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="E157" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="E158" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D158" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="E158" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D159" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="E159" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D159" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="E159" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="E160" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D160" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="E160" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D161" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="E161" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="E161" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C166" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C167" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C174" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E177" t="s" s="2">
         <v>308</v>
@@ -5050,359 +5077,410 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="B185" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D185" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="C185" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D185" t="s" s="2">
+      <c r="E185" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="E185" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D186" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="E186" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="E186" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="B187" t="s" s="2">
+      <c r="C187" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D187" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="C187" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D187" t="s" s="2">
+      <c r="E187" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="E187" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E188" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D188" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="E188" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="E189" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D189" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="E189" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="E190" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D190" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="E190" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="B191" t="s" s="2">
+      <c r="C191" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D191" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="C191" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D191" t="s" s="2">
+      <c r="E191" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="E191" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B192" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D192" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="C192" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D192" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="E192" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C193" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E193" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B194" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D194" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="C194" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D194" t="s" s="2">
+      <c r="E194" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="E194" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D195" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="E195" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D195" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="E195" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E196" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D196" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="E196" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="B197" t="s" s="2">
+      <c r="C197" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D197" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="C197" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D197" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="E197" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E198" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="B198" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C198" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D198" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="E198" t="s" s="2">
-        <v>358</v>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E199" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5451,461 +5529,461 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B7" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="C7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="E7" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -5946,7 +6024,7 @@
         <v>35</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>35</v>
@@ -5963,10 +6041,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4">
@@ -5980,10 +6058,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
@@ -5997,10 +6075,10 @@
         <v>39</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6">
@@ -6014,10 +6092,10 @@
         <v>39</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -6031,10 +6109,10 @@
         <v>39</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8">
@@ -6048,10 +6126,10 @@
         <v>39</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -6065,10 +6143,10 @@
         <v>39</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10">
@@ -6082,10 +6160,10 @@
         <v>39</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11">
@@ -6099,10 +6177,10 @@
         <v>39</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12">
@@ -6116,10 +6194,10 @@
         <v>39</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13">
@@ -6133,10 +6211,10 @@
         <v>39</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14">
@@ -6150,10 +6228,10 @@
         <v>39</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="15">
@@ -6167,10 +6245,10 @@
         <v>39</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16">
@@ -6184,10 +6262,10 @@
         <v>39</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17">
@@ -6201,10 +6279,10 @@
         <v>39</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="18">
@@ -6218,10 +6296,10 @@
         <v>39</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19">
@@ -6235,10 +6313,10 @@
         <v>39</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20">
@@ -6252,10 +6330,10 @@
         <v>39</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21">
@@ -6269,10 +6347,10 @@
         <v>39</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22">
@@ -6286,10 +6364,10 @@
         <v>39</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23">
@@ -6303,10 +6381,10 @@
         <v>39</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24">
@@ -6320,10 +6398,10 @@
         <v>39</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="25">
@@ -6337,10 +6415,10 @@
         <v>39</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26">
@@ -6354,10 +6432,10 @@
         <v>39</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27">
@@ -6371,10 +6449,10 @@
         <v>39</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28">
@@ -6388,10 +6466,10 @@
         <v>39</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29">
@@ -6405,10 +6483,10 @@
         <v>39</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30">
@@ -6422,10 +6500,10 @@
         <v>39</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31">
@@ -6439,10 +6517,10 @@
         <v>39</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32">
@@ -6456,10 +6534,10 @@
         <v>39</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33">
@@ -6473,10 +6551,10 @@
         <v>39</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34">
@@ -6490,10 +6568,10 @@
         <v>39</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="35">
@@ -6507,10 +6585,10 @@
         <v>39</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36">
@@ -6524,10 +6602,10 @@
         <v>39</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37">
@@ -6541,10 +6619,10 @@
         <v>39</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38">
@@ -6558,10 +6636,10 @@
         <v>39</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39">
@@ -6575,10 +6653,10 @@
         <v>39</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40">
@@ -6592,10 +6670,10 @@
         <v>39</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41">
@@ -6609,10 +6687,10 @@
         <v>39</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="42">
@@ -6626,10 +6704,10 @@
         <v>39</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="43">
@@ -6643,10 +6721,10 @@
         <v>39</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44">
@@ -6660,10 +6738,10 @@
         <v>39</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="45">
@@ -6677,10 +6755,10 @@
         <v>39</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="46">
@@ -6694,10 +6772,10 @@
         <v>39</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47">
@@ -6711,10 +6789,10 @@
         <v>39</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="48">
@@ -6728,10 +6806,10 @@
         <v>39</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49">
@@ -6745,10 +6823,10 @@
         <v>39</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50">
@@ -6762,10 +6840,10 @@
         <v>39</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="51">
@@ -6779,10 +6857,10 @@
         <v>39</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="52">
@@ -6796,10 +6874,10 @@
         <v>39</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53">
@@ -6813,10 +6891,10 @@
         <v>39</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54">
@@ -6830,10 +6908,10 @@
         <v>39</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55">
@@ -6847,10 +6925,10 @@
         <v>39</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="56">
@@ -6864,10 +6942,10 @@
         <v>39</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="57">
@@ -6881,10 +6959,10 @@
         <v>39</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="58">
@@ -6898,10 +6976,10 @@
         <v>39</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="59">
@@ -6915,10 +6993,10 @@
         <v>39</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60">
@@ -6932,10 +7010,10 @@
         <v>39</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61">
@@ -6949,10 +7027,10 @@
         <v>39</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62">
@@ -6966,10 +7044,10 @@
         <v>39</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="63">
@@ -6983,10 +7061,10 @@
         <v>39</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64">
@@ -7000,10 +7078,10 @@
         <v>39</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="65">
@@ -7017,10 +7095,10 @@
         <v>39</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="66">
@@ -7034,10 +7112,10 @@
         <v>39</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67">
@@ -7051,10 +7129,10 @@
         <v>39</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="68">
@@ -7068,10 +7146,10 @@
         <v>39</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69">
@@ -7085,10 +7163,10 @@
         <v>39</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="70">
@@ -7102,10 +7180,10 @@
         <v>39</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71">
@@ -7119,10 +7197,10 @@
         <v>39</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72">
@@ -7136,10 +7214,10 @@
         <v>39</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73">
@@ -7153,10 +7231,10 @@
         <v>39</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="74">
@@ -7170,10 +7248,10 @@
         <v>39</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75">
@@ -7187,10 +7265,10 @@
         <v>39</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76">
@@ -7204,10 +7282,10 @@
         <v>39</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="77">
@@ -7221,10 +7299,10 @@
         <v>39</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="78">
@@ -7238,10 +7316,10 @@
         <v>39</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="79">
@@ -7255,10 +7333,10 @@
         <v>39</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="80">
@@ -7272,10 +7350,10 @@
         <v>39</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
     <row r="81">
@@ -7289,10 +7367,10 @@
         <v>39</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="82">
@@ -7306,10 +7384,10 @@
         <v>39</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="83">
@@ -7323,10 +7401,10 @@
         <v>39</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="84">
@@ -7340,10 +7418,10 @@
         <v>39</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
     </row>
     <row r="85">
@@ -7357,10 +7435,10 @@
         <v>39</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="86">
@@ -7374,10 +7452,10 @@
         <v>39</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
     </row>
     <row r="87">
@@ -7391,10 +7469,10 @@
         <v>39</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="88">
@@ -7408,10 +7486,10 @@
         <v>39</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="89">
@@ -7425,10 +7503,10 @@
         <v>39</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="90">
@@ -7442,10 +7520,10 @@
         <v>39</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91">
@@ -7459,10 +7537,10 @@
         <v>39</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="92">
@@ -7476,10 +7554,10 @@
         <v>39</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
     </row>
     <row r="93">
@@ -7493,10 +7571,10 @@
         <v>39</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="94">
@@ -7510,10 +7588,10 @@
         <v>39</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="95">
@@ -7527,10 +7605,10 @@
         <v>39</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="96">
@@ -7544,10 +7622,10 @@
         <v>39</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="97">
@@ -7561,10 +7639,10 @@
         <v>39</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="98">
@@ -7578,10 +7656,10 @@
         <v>39</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="99">
@@ -7595,10 +7673,10 @@
         <v>39</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="100">
@@ -7612,10 +7690,10 @@
         <v>39</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="101">
@@ -7629,10 +7707,10 @@
         <v>39</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="102">
@@ -7646,10 +7724,10 @@
         <v>39</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="103">
@@ -7663,10 +7741,10 @@
         <v>39</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="104">
@@ -7680,10 +7758,10 @@
         <v>39</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="105">
@@ -7697,10 +7775,10 @@
         <v>39</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
     </row>
     <row r="106">
@@ -7714,10 +7792,10 @@
         <v>39</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
     </row>
     <row r="107">
@@ -7731,10 +7809,10 @@
         <v>39</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="108">
@@ -7748,10 +7826,10 @@
         <v>39</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="109">
@@ -7765,10 +7843,10 @@
         <v>39</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>541</v>
+        <v>550</v>
       </c>
     </row>
     <row r="110">
@@ -7782,10 +7860,10 @@
         <v>39</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="111">
@@ -7799,10 +7877,10 @@
         <v>39</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="112">
@@ -7816,10 +7894,10 @@
         <v>39</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
     </row>
     <row r="113">
@@ -7833,10 +7911,10 @@
         <v>39</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114">
@@ -7850,10 +7928,10 @@
         <v>39</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
     </row>
     <row r="115">
@@ -7867,10 +7945,10 @@
         <v>39</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="116">
@@ -7884,10 +7962,10 @@
         <v>39</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="117">
@@ -7901,10 +7979,10 @@
         <v>39</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="118">
@@ -7918,146 +7996,146 @@
         <v>39</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>565</v>
+        <v>574</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>567</v>
+        <v>576</v>
       </c>
     </row>
     <row r="127">
@@ -8071,95 +8149,95 @@
         <v>39</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>569</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C132" t="s" s="2">
         <v>39</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
